--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -22829,16 +22829,16 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O135" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>1.143402255037307</v>
+        <v>1.145340224961099</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -25645,16 +25645,16 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O152" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>0.1511616540557796</v>
+        <v>0.1666654134461159</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42890</v>
+        <v>42899</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -24317,16 +24317,16 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O141" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>1.145340224961099</v>
+        <v>1.147278194884891</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -27133,16 +27133,16 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O158" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2480601502453819</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27755,6 +27755,154 @@
       <c r="BC161" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>94</v>
+      </c>
+      <c r="O162" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.07677999031118203</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27791,7 +27939,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -27874,7 +28022,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -27884,7 +28032,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -27936,7 +28084,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42938</v>
+        <v>43036</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1454,9 +1451,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1850,9 +1844,6 @@
       <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -1998,9 +1989,6 @@
       <c r="O9" t="n">
         <v>329</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.6375921049275831</v>
       </c>
@@ -2146,9 +2134,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2791,7 +2776,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2938,9 +2923,6 @@
       <c r="O14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -4962,9 +4944,6 @@
       <c r="O27" t="n">
         <v>4</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5503,9 +5482,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5899,9 +5875,6 @@
       <c r="O32" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -6047,9 +6020,6 @@
       <c r="O33" t="n">
         <v>304</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.589142856832782</v>
       </c>
@@ -6195,9 +6165,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6840,7 +6807,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -6987,9 +6954,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8715,9 +8679,6 @@
       <c r="O49" t="n">
         <v>5</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="S49" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9256,9 +9217,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -9652,9 +9610,6 @@
       <c r="O54" t="n">
         <v>5</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -9800,9 +9755,6 @@
       <c r="O55" t="n">
         <v>371</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.718986841726849</v>
       </c>
@@ -9948,9 +9900,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10593,7 +10542,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -10740,9 +10689,6 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -12468,9 +12414,6 @@
       <c r="O71" t="n">
         <v>8</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.02938249455615832</v>
       </c>
@@ -12616,9 +12559,6 @@
       <c r="O72" t="n">
         <v>4</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13157,9 +13097,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -13553,9 +13490,6 @@
       <c r="O77" t="n">
         <v>2</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -13701,9 +13635,6 @@
       <c r="O78" t="n">
         <v>475</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.9205357138012219</v>
       </c>
@@ -13849,9 +13780,6 @@
       <c r="O79" t="n">
         <v>3</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -14245,9 +14173,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14494,7 +14419,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -14641,9 +14566,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -16221,9 +16143,6 @@
       <c r="O93" t="n">
         <v>7</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.02570968273663853</v>
       </c>
@@ -16369,9 +16288,6 @@
       <c r="O94" t="n">
         <v>4</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16910,9 +16826,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17306,9 +17219,6 @@
       <c r="O99" t="n">
         <v>3</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -17454,9 +17364,6 @@
       <c r="O100" t="n">
         <v>574</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>1.112394736256634</v>
       </c>
@@ -17602,9 +17509,6 @@
       <c r="O101" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -17998,9 +17902,6 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.01891260466471829</v>
       </c>
@@ -18247,7 +18148,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -18394,9 +18295,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -18790,9 +18688,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -20418,9 +20313,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -20714,9 +20606,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21110,9 +20999,6 @@
       <c r="O122" t="n">
         <v>4</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -21258,9 +21144,6 @@
       <c r="O123" t="n">
         <v>644</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>1.248052630922078</v>
       </c>
@@ -21406,9 +21289,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -21802,9 +21682,6 @@
       <c r="O126" t="n">
         <v>2</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -22051,7 +21928,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -22198,9 +22075,6 @@
       <c r="O128" t="n">
         <v>2</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -22594,9 +22468,6 @@
       <c r="O130" t="n">
         <v>114</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.09311615846249736</v>
       </c>
@@ -22742,9 +22613,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -22890,9 +22758,6 @@
       <c r="O132" t="n">
         <v>88</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.07187913986578744</v>
       </c>
@@ -23038,9 +22903,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -23186,9 +23048,6 @@
       <c r="O134" t="n">
         <v>100</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.08168084075657663</v>
       </c>
@@ -23334,9 +23193,6 @@
       <c r="O135" t="n">
         <v>2</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -23482,9 +23338,6 @@
       <c r="O136" t="n">
         <v>104</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.0849480743868397</v>
       </c>
@@ -23630,9 +23483,6 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -23778,9 +23628,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -23926,9 +23773,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -24317,16 +24161,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O141" t="n">
-        <v>592</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="R141" t="n">
-        <v>1.147278194884891</v>
+        <v>1.149216164808683</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24470,9 +24311,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -24866,9 +24704,6 @@
       <c r="O144" t="n">
         <v>2</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -25262,9 +25097,6 @@
       <c r="O146" t="n">
         <v>119</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.09720020050032618</v>
       </c>
@@ -25410,9 +25242,6 @@
       <c r="O147" t="n">
         <v>1</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -25558,9 +25387,6 @@
       <c r="O148" t="n">
         <v>107</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.08739849960953699</v>
       </c>
@@ -25706,9 +25532,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -25854,9 +25677,6 @@
       <c r="O150" t="n">
         <v>104</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.0849480743868397</v>
       </c>
@@ -26002,9 +25822,6 @@
       <c r="O151" t="n">
         <v>3</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -26150,9 +25967,6 @@
       <c r="O152" t="n">
         <v>135</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.1102691350213785</v>
       </c>
@@ -26298,9 +26112,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -26446,9 +26257,6 @@
       <c r="O154" t="n">
         <v>84</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.06861190623552436</v>
       </c>
@@ -26594,9 +26402,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -26742,9 +26547,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -27133,16 +26935,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="O158" t="n">
-        <v>128</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="R158" t="n">
-        <v>0.2480601502453819</v>
+        <v>0.2984473682639751</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27286,9 +27085,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -27682,9 +27478,6 @@
       <c r="O161" t="n">
         <v>1</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -27830,9 +27623,6 @@
       <c r="O162" t="n">
         <v>94</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.07677999031118203</v>
       </c>
@@ -27903,6 +27693,151 @@
       <c r="BC162" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="n">
+        <v>1</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27874,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -28022,7 +27957,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -28032,7 +27967,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -28084,7 +28019,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43036</v>
+        <v>43064</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -26935,13 +26935,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="O158" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="R158" t="n">
-        <v>0.2984473682639751</v>
+        <v>0.3061992479591433</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43064</v>
+        <v>43068</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -16439,10 +16439,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -20414,12 +20414,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20453,84 +20453,92 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>7685</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>7685</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0.5439113434107427</v>
+        <v>0</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MUMPS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MUMPS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20557,17 +20565,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20606,17 +20614,34 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_171</t>
+          <t>SER_CA_ON_PHO_IDTO_MUMPS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MUMPS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -20624,6 +20649,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary mumps notifications combining confirmed and probable cases under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20636,12 +20719,12 @@
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_171</t>
+          <t>SER_CA_ON_PHO_IDTO_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
@@ -20649,47 +20732,47 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20716,17 +20799,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20760,170 +20843,84 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>7685</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
-        <v>1</v>
+        <v>7685</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.5439113434107427</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20955,12 +20952,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20994,81 +20991,95 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0.05421081120786837</v>
+        <v>0</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21095,17 +21106,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21139,81 +21150,170 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>644</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>644</v>
-      </c>
-      <c r="R123" t="n">
-        <v>1.248052630922078</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21245,12 +21345,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21284,95 +21384,81 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R124" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05421081120786837</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21399,17 +21485,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21443,170 +21529,81 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>644</v>
       </c>
       <c r="O125" t="n">
-        <v>1</v>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>1</v>
+        <v>644</v>
+      </c>
+      <c r="R125" t="n">
+        <v>1.248052630922078</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21638,12 +21635,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21677,13 +21674,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>0.03782520932943658</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -21692,7 +21689,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -21717,7 +21714,7 @@
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="AT126" t="n">
@@ -21730,42 +21727,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21797,12 +21794,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21836,29 +21833,29 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Kusma</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -21868,7 +21865,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -21883,7 +21880,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
@@ -21918,17 +21915,17 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly mumps notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -21951,7 +21948,7 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -21964,42 +21961,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22031,12 +22028,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22076,7 +22073,7 @@
         <v>2</v>
       </c>
       <c r="R128" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.03782520932943658</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22085,7 +22082,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -22110,7 +22107,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -22123,42 +22120,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22190,12 +22187,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22236,22 +22233,22 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>Påssjuka</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -22261,7 +22258,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -22276,7 +22273,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -22311,17 +22308,17 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly mumps notifications.</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -22344,7 +22341,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -22357,42 +22354,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22424,12 +22421,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22454,7 +22451,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22463,81 +22460,95 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="O130" t="n">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="R130" t="n">
-        <v>0.09311615846249736</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22564,17 +22575,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22599,7 +22610,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22608,81 +22619,170 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Påssjuka</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22744,7 +22844,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22753,13 +22853,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="O132" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="R132" t="n">
-        <v>0.07187913986578744</v>
+        <v>0.09311615846249736</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22889,7 +22989,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -23034,7 +23134,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -23043,13 +23143,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="O134" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R134" t="n">
-        <v>0.08168084075657663</v>
+        <v>0.07187913986578744</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23179,7 +23279,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -23188,13 +23288,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23324,7 +23424,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -23333,13 +23433,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O136" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="R136" t="n">
-        <v>0.0849480743868397</v>
+        <v>0.08168084075657663</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23469,7 +23569,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23478,13 +23578,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R137" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23584,12 +23684,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23614,22 +23714,22 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>0.0849480743868397</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23662,42 +23762,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23729,12 +23829,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23759,104 +23859,90 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ139" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23883,17 +23969,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23932,165 +24018,76 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN140" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP140" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AT140" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV140" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24122,12 +24119,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24161,81 +24158,95 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>1.149216164808683</v>
+        <v>0</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24262,17 +24273,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24311,17 +24322,34 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -24329,6 +24357,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -24341,12 +24427,12 @@
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -24354,47 +24440,47 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24421,17 +24507,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24465,170 +24551,81 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN143" t="b">
-        <v>1</v>
+        <v>593</v>
+      </c>
+      <c r="R143" t="n">
+        <v>1.149216164808683</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24660,12 +24657,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24699,13 +24696,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0.01868976085656669</v>
+        <v>0</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24714,7 +24711,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -24739,7 +24736,7 @@
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -24752,42 +24749,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24819,12 +24816,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24858,29 +24855,29 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>Påssjuka</t>
+          <t>Kusma</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -24905,7 +24902,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -24940,17 +24937,17 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -24973,7 +24970,7 @@
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="AT145" t="n">
@@ -24986,42 +24983,42 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25053,12 +25050,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25083,7 +25080,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25092,81 +25089,95 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="O146" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="R146" t="n">
-        <v>0.09720020050032618</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25193,17 +25204,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25228,7 +25239,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25237,81 +25248,170 @@
         </is>
       </c>
       <c r="N147" t="n">
+        <v>2</v>
+      </c>
+      <c r="O147" t="n">
+        <v>2</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Påssjuka</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN147" t="b">
         <v>1</v>
       </c>
-      <c r="O147" t="n">
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT147" t="n">
         <v>1</v>
       </c>
-      <c r="R147" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP147" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
-      <c r="AT147" t="n">
-        <v>0</v>
-      </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25373,7 +25473,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25382,13 +25482,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O148" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="R148" t="n">
-        <v>0.08739849960953699</v>
+        <v>0.09720020050032618</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25518,7 +25618,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25663,7 +25763,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25672,13 +25772,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="O150" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="R150" t="n">
-        <v>0.0849480743868397</v>
+        <v>0.08739849960953699</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25808,7 +25908,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25817,13 +25917,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R151" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25953,7 +26053,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -25962,13 +26062,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="O152" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="R152" t="n">
-        <v>0.1102691350213785</v>
+        <v>0.0849480743868397</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26098,7 +26198,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26107,13 +26207,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26243,7 +26343,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26252,13 +26352,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="O154" t="n">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="R154" t="n">
-        <v>0.06861190623552436</v>
+        <v>0.1102691350213785</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26358,12 +26458,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26388,12 +26488,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N155" t="n">
@@ -26436,42 +26536,42 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26503,12 +26603,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26533,104 +26633,90 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>0.06861190623552436</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26657,17 +26743,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26706,165 +26792,76 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP157" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AT157" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV157" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26896,12 +26893,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26935,81 +26932,95 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>0.3061992479591433</v>
+        <v>0</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27036,17 +27047,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27085,17 +27096,34 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -27103,6 +27131,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27115,12 +27201,12 @@
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
       <c r="AT159" t="n">
@@ -27128,47 +27214,47 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27195,17 +27281,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27239,170 +27325,81 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN160" t="b">
-        <v>1</v>
+        <v>158</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.3061992479591433</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27434,12 +27431,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27473,81 +27470,95 @@
         </is>
       </c>
       <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT161" t="n">
         <v>1</v>
       </c>
-      <c r="O161" t="n">
-        <v>1</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP161" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
-      <c r="AT161" t="n">
-        <v>0</v>
-      </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27574,17 +27585,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27609,7 +27620,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -27618,81 +27629,170 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>94</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0.07677999031118203</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27854,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -27836,6 +27936,296 @@
         </is>
       </c>
       <c r="BC163" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>94</v>
+      </c>
+      <c r="O164" t="n">
+        <v>94</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.07677999031118203</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -27957,7 +28347,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -27967,7 +28357,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -27987,7 +28377,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -28019,7 +28409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43068</v>
+        <v>43067</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -27325,13 +27325,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="O160" t="n">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="R160" t="n">
-        <v>0.3061992479591433</v>
+        <v>0.3953458644535773</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -28228,6 +28228,151 @@
       <c r="BC165" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>73</v>
+      </c>
+      <c r="O166" t="n">
+        <v>73</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.05962701375230094</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28409,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -28347,7 +28492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -28357,7 +28502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -28409,7 +28554,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43067</v>
+        <v>43186</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -24119,12 +24119,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24158,95 +24158,84 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>5818</v>
       </c>
       <c r="O141" t="n">
+        <v>5818</v>
+      </c>
+      <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>0.4117730899106963</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -24273,7 +24262,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -24322,98 +24311,23 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN142" t="b">
-        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -24507,17 +24421,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24551,81 +24465,170 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>593</v>
-      </c>
-      <c r="R143" t="n">
-        <v>1.149216164808683</v>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24657,12 +24660,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24696,95 +24699,81 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>1.149216164808683</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24811,7 +24800,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -24860,98 +24849,23 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN145" t="b">
-        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -25045,17 +24959,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25089,22 +25003,39 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>2</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0.01868976085656669</v>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -25112,6 +25043,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -25129,7 +25118,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -25142,42 +25131,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25204,7 +25193,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -25253,98 +25242,23 @@
       <c r="O147" t="n">
         <v>2</v>
       </c>
+      <c r="R147" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MUMPS</t>
         </is>
       </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Påssjuka</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN147" t="b">
-        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -25438,17 +25352,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25473,7 +25387,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25482,81 +25396,170 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="O148" t="n">
-        <v>119</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0.09720020050032618</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Påssjuka</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25588,12 +25591,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25627,13 +25630,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="O149" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="R149" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.09720020050032618</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25666,42 +25669,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25733,12 +25736,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25763,7 +25766,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25772,13 +25775,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="O150" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="R150" t="n">
-        <v>0.08739849960953699</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25811,42 +25814,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25878,12 +25881,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25917,13 +25920,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="O151" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="R151" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.08739849960953699</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25956,42 +25959,42 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26023,12 +26026,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26053,7 +26056,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26062,13 +26065,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="O152" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="R152" t="n">
-        <v>0.0849480743868397</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26101,42 +26104,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26168,12 +26171,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26207,13 +26210,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="O153" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="R153" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.0849480743868397</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26246,42 +26249,42 @@
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26313,12 +26316,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26343,7 +26346,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26352,13 +26355,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="O154" t="n">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="R154" t="n">
-        <v>0.1102691350213785</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26391,42 +26394,42 @@
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26458,12 +26461,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26497,13 +26500,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>0.1102691350213785</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26536,42 +26539,42 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26603,12 +26606,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26633,7 +26636,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26642,13 +26645,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>0.06861190623552436</v>
+        <v>0</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26681,42 +26684,42 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26748,12 +26751,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26778,22 +26781,22 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>0.06861190623552436</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -26826,42 +26829,42 @@
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26893,12 +26896,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26945,82 +26948,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27036,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -27096,98 +27085,23 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
@@ -27281,17 +27195,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27325,81 +27239,170 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>204</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0.3953458644535773</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27431,12 +27434,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27470,95 +27473,81 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>0.3953458644535773</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27585,7 +27574,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -27634,98 +27623,23 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
@@ -27819,17 +27733,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27863,81 +27777,170 @@
         </is>
       </c>
       <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
         <v>1</v>
       </c>
-      <c r="O163" t="n">
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
         <v>1</v>
       </c>
-      <c r="R163" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP163" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
-      <c r="AT163" t="n">
-        <v>0</v>
-      </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27969,12 +27972,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27999,7 +28002,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -28008,13 +28011,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="O164" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="R164" t="n">
-        <v>0.07677999031118203</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -28047,42 +28050,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28114,12 +28117,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28144,7 +28147,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -28153,13 +28156,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="O165" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="R165" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.07677999031118203</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -28192,42 +28195,42 @@
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28259,12 +28262,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28289,7 +28292,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -28298,13 +28301,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="O166" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="R166" t="n">
-        <v>0.05962701375230094</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -28337,40 +28340,185 @@
       </c>
       <c r="AV166" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>73</v>
+      </c>
+      <c r="O167" t="n">
+        <v>73</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.05962701375230094</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW166" t="inlineStr">
+      <c r="AW167" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX166" t="inlineStr">
+      <c r="AX167" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY166" t="inlineStr">
+      <c r="AY167" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ166" t="inlineStr">
+      <c r="AZ167" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA166" t="inlineStr">
+      <c r="BA167" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB166" t="inlineStr">
+      <c r="BB167" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC166" t="inlineStr">
+      <c r="BC167" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -28492,7 +28640,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -28502,7 +28650,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -28554,7 +28702,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43186</v>
+        <v>49004</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -27080,13 +27080,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27239,10 +27239,10 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49004</v>
+        <v>49005</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -22067,13 +22067,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R128" t="n">
-        <v>0.03782520932943658</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22226,10 +22226,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -25198,12 +25198,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25237,13 +25237,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>0.01868976085656669</v>
+        <v>0</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -25277,7 +25277,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -25290,42 +25290,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25357,12 +25357,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25396,29 +25396,29 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>Påssjuka</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
@@ -25478,17 +25478,17 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly mumps notifications.</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -25524,42 +25524,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25591,12 +25591,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25621,7 +25621,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25630,81 +25630,95 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="O149" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="R149" t="n">
-        <v>0.09720020050032618</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25731,17 +25745,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25766,7 +25780,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25775,81 +25789,170 @@
         </is>
       </c>
       <c r="N150" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" t="n">
+        <v>2</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Påssjuka</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
         <v>1</v>
       </c>
-      <c r="O150" t="n">
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
         <v>1</v>
       </c>
-      <c r="R150" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP150" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
-      <c r="AT150" t="n">
-        <v>0</v>
-      </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25911,7 +26014,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25920,13 +26023,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O151" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="R151" t="n">
-        <v>0.08739849960953699</v>
+        <v>0.09720020050032618</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -26056,7 +26159,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26201,7 +26304,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26210,13 +26313,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="O153" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="R153" t="n">
-        <v>0.0849480743868397</v>
+        <v>0.08739849960953699</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26346,7 +26449,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26355,13 +26458,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R154" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26491,7 +26594,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -26500,13 +26603,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="O155" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="R155" t="n">
-        <v>0.1102691350213785</v>
+        <v>0.0849480743868397</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26636,7 +26739,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26645,13 +26748,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26781,7 +26884,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -26790,13 +26893,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="O157" t="n">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="R157" t="n">
-        <v>0.06861190623552436</v>
+        <v>0.1102691350213785</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -26896,12 +26999,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26926,12 +27029,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N158" t="n">
@@ -26974,42 +27077,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27041,12 +27144,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27071,104 +27174,90 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="R159" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.06861190623552436</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27195,17 +27284,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27239,170 +27328,81 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>1</v>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN160" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP160" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AT160" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV160" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27434,12 +27434,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27473,81 +27473,95 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>204</v>
+        <v>2</v>
       </c>
       <c r="O161" t="n">
-        <v>204</v>
+        <v>2</v>
       </c>
       <c r="R161" t="n">
-        <v>0.3953458644535773</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27574,17 +27588,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27618,22 +27632,39 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -27641,6 +27672,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27653,12 +27742,12 @@
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
       <c r="AT162" t="n">
@@ -27666,47 +27755,47 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27733,17 +27822,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27777,170 +27866,81 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="O163" t="n">
-        <v>0</v>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN163" t="b">
-        <v>1</v>
+        <v>320</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.6201503756134548</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27972,12 +27972,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28011,81 +28011,95 @@
         </is>
       </c>
       <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
         <v>1</v>
       </c>
-      <c r="O164" t="n">
-        <v>1</v>
-      </c>
-      <c r="R164" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP164" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
-      <c r="AT164" t="n">
-        <v>0</v>
-      </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28112,17 +28126,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28147,7 +28161,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -28156,81 +28170,170 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>94</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0.07677999031118203</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28395,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -28437,7 +28540,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28446,13 +28549,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="O167" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="R167" t="n">
-        <v>0.05962701375230094</v>
+        <v>0.07677999031118203</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -28519,6 +28622,441 @@
         </is>
       </c>
       <c r="BC167" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="n">
+        <v>1</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
+      <c r="AT168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>73</v>
+      </c>
+      <c r="O169" t="n">
+        <v>73</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.05962701375230094</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>64</v>
+      </c>
+      <c r="O170" t="n">
+        <v>64</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.05227573808420904</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -28557,7 +29095,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -28640,7 +29178,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -28650,7 +29188,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -28670,7 +29208,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -28702,7 +29240,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49005</v>
+        <v>49185</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -27866,13 +27866,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O163" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="R163" t="n">
-        <v>0.6201503756134548</v>
+        <v>0.6240263154610388</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49185</v>
+        <v>49187</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -34904,12 +34904,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34943,13 +34943,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>1.149216164808683</v>
+        <v>0</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -34982,42 +34982,42 @@
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35049,12 +35049,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -35088,95 +35088,81 @@
         </is>
       </c>
       <c r="N197" t="n">
+        <v>593</v>
+      </c>
+      <c r="O197" t="n">
+        <v>593</v>
+      </c>
+      <c r="R197" t="n">
+        <v>1.149216164808683</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="n">
         <v>0</v>
       </c>
-      <c r="O197" t="n">
-        <v>0</v>
-      </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP197" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT197" t="n">
-        <v>1</v>
-      </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35203,7 +35189,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -35252,98 +35238,23 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U198" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -35437,17 +35348,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35486,17 +35397,34 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -35504,6 +35432,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35521,7 +35507,7 @@
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="AT199" t="n">
@@ -35534,42 +35520,42 @@
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -35596,7 +35582,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -35645,98 +35631,23 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U200" t="inlineStr">
         <is>
           <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly mumps notifications.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -35830,17 +35741,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35874,22 +35785,39 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>2</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0.01868976085656669</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -35897,6 +35825,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly mumps notifications.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35914,7 +35900,7 @@
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
@@ -35927,42 +35913,42 @@
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35989,7 +35975,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -36038,98 +36024,23 @@
       <c r="O202" t="n">
         <v>2</v>
       </c>
+      <c r="R202" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MUMPS</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Påssjuka</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -36223,17 +36134,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -36258,7 +36169,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -36267,81 +36178,170 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="O203" t="n">
-        <v>119</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0.09720020050032618</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Påssjuka</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -36373,12 +36373,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -36412,13 +36412,13 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="O204" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="R204" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.09720020050032618</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -36451,42 +36451,42 @@
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36518,12 +36518,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -36548,7 +36548,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -36557,93 +36557,81 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O205" t="n">
-        <v>3</v>
-      </c>
-      <c r="P205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R205" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36670,7 +36658,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -36722,98 +36710,18 @@
       <c r="P206" t="n">
         <v>3</v>
       </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R206" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -36907,17 +36815,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36942,7 +36850,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -36951,81 +36859,173 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>107</v>
+        <v>3</v>
       </c>
       <c r="O207" t="n">
-        <v>107</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0.08739849960953699</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P207" t="n">
+        <v>3</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37057,12 +37057,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -37096,13 +37096,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="O208" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="R208" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.08739849960953699</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -37135,42 +37135,42 @@
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37202,12 +37202,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -37232,7 +37232,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -37241,93 +37241,81 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O209" t="n">
-        <v>3</v>
-      </c>
-      <c r="P209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R209" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37354,7 +37342,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -37406,98 +37394,18 @@
       <c r="P210" t="n">
         <v>3</v>
       </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R210" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -37591,17 +37499,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -37626,7 +37534,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -37635,81 +37543,173 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="O211" t="n">
-        <v>104</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0.0849480743868397</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P211" t="n">
+        <v>3</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37741,12 +37741,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -37780,13 +37780,13 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="O212" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="R212" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.0849480743868397</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -37819,42 +37819,42 @@
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37886,12 +37886,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -37916,7 +37916,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -37925,93 +37925,81 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O213" t="n">
-        <v>4</v>
-      </c>
-      <c r="P213" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R213" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38038,7 +38026,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -38090,98 +38078,18 @@
       <c r="P214" t="n">
         <v>4</v>
       </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R214" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN214" t="b">
-        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -38275,17 +38183,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -38310,7 +38218,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -38319,81 +38227,173 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>135</v>
+        <v>4</v>
       </c>
       <c r="O215" t="n">
-        <v>135</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0.1102691350213785</v>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P215" t="n">
+        <v>4</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>1</v>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38425,12 +38425,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -38464,13 +38464,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>0.1102691350213785</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -38503,42 +38503,42 @@
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38570,12 +38570,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -38600,7 +38600,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -38609,13 +38609,13 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>0.06861190623552436</v>
+        <v>0</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -38648,42 +38648,42 @@
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38715,12 +38715,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -38754,93 +38754,81 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="O218" t="n">
-        <v>3</v>
-      </c>
-      <c r="P218" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="R218" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.06861190623552436</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ218" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38867,7 +38855,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -38919,98 +38907,18 @@
       <c r="P219" t="n">
         <v>3</v>
       </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R219" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE219" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF219" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG219" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM219" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN219" t="b">
-        <v>1</v>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
@@ -39104,17 +39012,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39139,90 +39047,182 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
-      </c>
-      <c r="R220" t="n">
-        <v>0</v>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P220" t="n">
+        <v>3</v>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM220" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN220" t="b">
+        <v>1</v>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39254,12 +39254,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -39293,95 +39293,81 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>0.03557618341728275</v>
+        <v>0</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr"/>
       <c r="AT221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39408,7 +39394,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -39457,98 +39443,23 @@
       <c r="O222" t="n">
         <v>2</v>
       </c>
+      <c r="R222" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U222" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN222" t="b">
-        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
@@ -39642,17 +39553,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -39686,81 +39597,170 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>322</v>
+        <v>2</v>
       </c>
       <c r="O223" t="n">
-        <v>322</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0.6240263154610388</v>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
+        <v>1</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -39792,12 +39792,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -39831,95 +39831,81 @@
         </is>
       </c>
       <c r="N224" t="n">
+        <v>337</v>
+      </c>
+      <c r="O224" t="n">
+        <v>337</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0.6530958643179194</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr"/>
+      <c r="AT224" t="n">
         <v>0</v>
       </c>
-      <c r="O224" t="n">
-        <v>0</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0</v>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA224" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO224" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP224" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ224" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT224" t="n">
-        <v>1</v>
-      </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -39946,7 +39932,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -39995,98 +39981,23 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U225" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE225" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG225" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM225" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN225" t="b">
-        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
@@ -40180,17 +40091,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40224,81 +40135,170 @@
         </is>
       </c>
       <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
         <v>1</v>
       </c>
-      <c r="O226" t="n">
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
         <v>1</v>
       </c>
-      <c r="R226" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP226" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
-      <c r="AT226" t="n">
-        <v>0</v>
-      </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40330,12 +40330,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -40360,7 +40360,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -40369,13 +40369,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="O227" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="R227" t="n">
-        <v>0.07677999031118203</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -40408,42 +40408,42 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40475,12 +40475,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40514,93 +40514,81 @@
         </is>
       </c>
       <c r="N228" t="n">
+        <v>94</v>
+      </c>
+      <c r="O228" t="n">
+        <v>94</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0.07677999031118203</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
+      <c r="AT228" t="n">
         <v>0</v>
       </c>
-      <c r="O228" t="n">
-        <v>0</v>
-      </c>
-      <c r="P228" t="n">
-        <v>0</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA228" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO228" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP228" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
-      <c r="AT228" t="n">
-        <v>2</v>
-      </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40627,7 +40615,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -40679,98 +40667,18 @@
       <c r="P229" t="n">
         <v>0</v>
       </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W229" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X229" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD229" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE229" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF229" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG229" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK229" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM229" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN229" t="b">
-        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
@@ -40864,17 +40772,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -40899,7 +40807,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -40908,81 +40816,173 @@
         </is>
       </c>
       <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
         <v>1</v>
       </c>
-      <c r="O230" t="n">
-        <v>1</v>
-      </c>
-      <c r="R230" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41014,12 +41014,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -41044,7 +41044,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -41053,13 +41053,13 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="O231" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="R231" t="n">
-        <v>0.05962701375230094</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -41092,42 +41092,42 @@
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41159,12 +41159,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -41198,93 +41198,81 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="O232" t="n">
-        <v>4</v>
-      </c>
-      <c r="P232" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="R232" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.05962701375230094</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41311,7 +41299,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -41363,98 +41351,18 @@
       <c r="P233" t="n">
         <v>4</v>
       </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R233" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE233" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF233" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG233" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK233" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM233" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN233" t="b">
-        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
@@ -41548,17 +41456,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -41583,7 +41491,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -41592,81 +41500,173 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="O234" t="n">
-        <v>64</v>
-      </c>
-      <c r="R234" t="n">
-        <v>0.05227573808420904</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P234" t="n">
+        <v>4</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41698,12 +41698,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -41737,93 +41737,81 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="O235" t="n">
-        <v>3</v>
-      </c>
-      <c r="P235" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="R235" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.05227573808420904</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA235" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41850,7 +41838,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -41902,98 +41890,18 @@
       <c r="P236" t="n">
         <v>3</v>
       </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W236" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X236" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R236" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD236" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE236" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF236" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG236" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM236" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN236" t="b">
-        <v>1</v>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
@@ -42059,6 +41967,243 @@
         </is>
       </c>
       <c r="BC236" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>3</v>
+      </c>
+      <c r="O237" t="n">
+        <v>3</v>
+      </c>
+      <c r="P237" t="n">
+        <v>3</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM237" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN237" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV237" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA237" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -42180,7 +42325,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -42190,7 +42335,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -42242,7 +42387,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49333</v>
+        <v>49348</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -68174,13 +68174,13 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R376" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S376" t="inlineStr">
         <is>
@@ -68722,13 +68722,13 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O379" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R379" t="n">
-        <v>0.04457330824721705</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
@@ -69381,7 +69381,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67119</v>
+        <v>67122</v>
       </c>
     </row>
     <row r="16">
